--- a/database/controller_excel/FO-DSP-TI-04 Programa de Auditoria de Herramientas de Trabajo Región XX Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-04 Programa de Auditoria de Herramientas de Trabajo Región XX Rev.00.xlsx
@@ -1,12 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Inventario_TI\database\controller_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5772"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Auditoria Htas TI" sheetId="1" r:id="rId4"/>
+    <sheet name="Auditoria Htas TI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -118,77 +126,82 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="14">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -198,7 +211,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -214,53 +227,79 @@
     </fill>
   </fills>
   <borders count="15">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -270,32 +309,47 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -310,128 +364,144 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -442,11 +512,11 @@
     <xdr:ext cx="857250" cy="857250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="2" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -464,7 +534,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -654,29 +724,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:S31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.71"/>
-    <col customWidth="1" min="2" max="2" width="5.43"/>
-    <col customWidth="1" min="3" max="3" width="15.57"/>
-    <col customWidth="1" min="4" max="4" width="18.14"/>
-    <col customWidth="1" min="5" max="5" width="18.57"/>
-    <col customWidth="1" min="6" max="6" width="27.86"/>
-    <col customWidth="1" min="7" max="7" width="21.0"/>
-    <col customWidth="1" min="8" max="19" width="5.14"/>
-    <col customWidth="1" min="20" max="20" width="4.57"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="6" max="6" width="27.88671875" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="19" width="5.109375" customWidth="1"/>
+    <col min="20" max="20" width="4.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.0" customHeight="1">
+    <row r="1" spans="1:19" ht="18" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -697,593 +769,671 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" ht="18.0" customHeight="1">
+    <row r="2" spans="1:19" ht="18" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="8" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="10"/>
-    </row>
-    <row r="3" ht="18.0" customHeight="1">
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="31"/>
+    </row>
+    <row r="3" spans="1:19" ht="18" customHeight="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="11"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="13" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="10"/>
-    </row>
-    <row r="4">
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="31"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.4">
       <c r="A4" s="3"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="13" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="10"/>
-    </row>
-    <row r="5" ht="18.0" customHeight="1">
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="31"/>
+    </row>
+    <row r="5" spans="1:19" ht="18" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="5"/>
-    </row>
-    <row r="6" ht="18.0" customHeight="1">
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="20"/>
+    </row>
+    <row r="6" spans="1:19" ht="18" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="16"/>
-    </row>
-    <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-    </row>
-    <row r="8" ht="33.75" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="24"/>
+    </row>
+    <row r="7" spans="1:19" ht="18" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+    </row>
+    <row r="8" spans="1:19" ht="33.75" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+    </row>
+    <row r="9" spans="1:19" ht="19.5" customHeight="1">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-    </row>
-    <row r="11" ht="18.0" customHeight="1">
-      <c r="A11" s="17"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+    </row>
+    <row r="10" spans="1:19" ht="19.5" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+    </row>
+    <row r="11" spans="1:19" ht="18" customHeight="1">
+      <c r="A11" s="4"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="35" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" ht="18.0" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="22" t="s">
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+    </row>
+    <row r="12" spans="1:19" ht="18" customHeight="1">
+      <c r="A12" s="4"/>
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N12" s="22" t="s">
+      <c r="N12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P12" s="22" t="s">
+      <c r="P12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="R12" s="22" t="s">
+      <c r="R12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="22" t="s">
+      <c r="S12" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="26"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="29"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="26"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="29"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="26"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A14" s="14"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="11"/>
+    </row>
+    <row r="15" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A15" s="14"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="11"/>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="33" t="s">
         <v>28</v>
       </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="1"/>
       <c r="I17" s="33" t="s">
         <v>29</v>
       </c>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
       <c r="F20" s="1"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="33" t="s">
         <v>30</v>
       </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="1"/>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="33" t="s">
         <v>31</v>
       </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
       <c r="F22" s="1"/>
       <c r="I22" s="33" t="s">
         <v>32</v>
       </c>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1">
       <c r="F23" s="1"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="38" t="s">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A25" s="18"/>
+      <c r="B25" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="31"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="16"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="N26" s="32"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="N26" s="17"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
@@ -1292,12 +1442,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:C6"/>
-    <mergeCell ref="D2:M4"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="D5:S6"/>
     <mergeCell ref="D8:S8"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C22:E22"/>
@@ -1311,10 +1455,16 @@
     <mergeCell ref="I20:P20"/>
     <mergeCell ref="I21:P21"/>
     <mergeCell ref="I22:P22"/>
+    <mergeCell ref="B2:C6"/>
+    <mergeCell ref="D2:M4"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="D5:S6"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database/controller_excel/FO-DSP-TI-04 Programa de Auditoria de Herramientas de Trabajo Región XX Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-04 Programa de Auditoria de Herramientas de Trabajo Región XX Rev.00.xlsx
@@ -438,6 +438,33 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -450,39 +477,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,118 +771,118 @@
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="29" t="s">
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="31"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="41"/>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="29" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="31"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="41"/>
     </row>
     <row r="4" spans="1:19" ht="14.4">
       <c r="A4" s="3"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="29" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="31"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="20"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="31"/>
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="24"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="35"/>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1">
       <c r="A7" s="4"/>
@@ -911,24 +911,24 @@
       <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
     </row>
     <row r="9" spans="1:19" ht="19.5" customHeight="1">
       <c r="A9" s="4"/>
@@ -936,24 +936,24 @@
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="19.5" customHeight="1">
       <c r="A10" s="4"/>
@@ -984,20 +984,20 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1">
       <c r="A12" s="4"/>
@@ -1143,22 +1143,22 @@
     <row r="17" spans="1:19" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="1"/>
-      <c r="I17" s="33" t="s">
+      <c r="I17" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -1208,18 +1208,18 @@
     <row r="20" spans="1:19" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
       <c r="F20" s="1"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -1227,22 +1227,22 @@
     <row r="21" spans="1:19" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="1"/>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -1250,22 +1250,22 @@
     <row r="22" spans="1:19" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="1"/>
-      <c r="I22" s="33" t="s">
+      <c r="I22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -1301,12 +1301,12 @@
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1">
       <c r="A25" s="18"/>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="16"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -1442,6 +1442,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:C6"/>
+    <mergeCell ref="D2:M4"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="D5:S6"/>
     <mergeCell ref="D8:S8"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C22:E22"/>
@@ -1455,16 +1461,10 @@
     <mergeCell ref="I20:P20"/>
     <mergeCell ref="I21:P21"/>
     <mergeCell ref="I22:P22"/>
-    <mergeCell ref="B2:C6"/>
-    <mergeCell ref="D2:M4"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="D5:S6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>